--- a/Заказ_666_реестр.xlsx
+++ b/Заказ_666_реестр.xlsx
@@ -1,17 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="отправкиоплаты" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="отправкиоплаты" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>№ заказа</t>
+  </si>
+  <si>
+    <t>договор</t>
+  </si>
+  <si>
+    <t>учет</t>
+  </si>
+  <si>
+    <t>модель</t>
+  </si>
+  <si>
+    <t>заказано</t>
+  </si>
+  <si>
+    <t>цена</t>
+  </si>
+  <si>
+    <t>документы</t>
+  </si>
+  <si>
+    <t>цех</t>
+  </si>
+  <si>
+    <t>статус</t>
+  </si>
+  <si>
+    <t>дата отправки</t>
+  </si>
+  <si>
+    <t>кол-во</t>
+  </si>
+  <si>
+    <t>мест</t>
+  </si>
+  <si>
+    <t>вес</t>
+  </si>
+  <si>
+    <t>сумма отправки</t>
+  </si>
+  <si>
+    <t>документы отправки</t>
+  </si>
+  <si>
+    <t>водитель</t>
+  </si>
+  <si>
+    <t>сумма заказа</t>
+  </si>
+  <si>
+    <t>предоплата</t>
+  </si>
+  <si>
+    <t>фактическая постоплата</t>
+  </si>
+  <si>
+    <t>предполагаемая постоплата</t>
+  </si>
+  <si>
+    <t>недоплата</t>
+  </si>
+  <si>
+    <t>доп постоплата</t>
+  </si>
+  <si>
+    <t>Аи 13.04.26/4</t>
+  </si>
+  <si>
+    <t>666/1-1</t>
+  </si>
+  <si>
+    <t>Костюм_руб_с_кор_рук_и_шорт_Учет_Бишкек_NEW_Айзада_Az.pdf</t>
+  </si>
+  <si>
+    <t>костюм летний с шортами сингапур</t>
+  </si>
+  <si>
+    <t>Аи 13.04.26/4_666</t>
+  </si>
+  <si>
+    <t>отправлено</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>отправка 666.pdf</t>
+  </si>
+  <si>
+    <t>Ташыкулов Элмир Койчубаевич</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21,30 +118,40 @@
   </numFmts>
   <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="001155CC"/>
-      <u val="single"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,115 +165,46 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -454,245 +492,178 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:V2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="46.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="28.7109375" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="24.7109375" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>№ заказа</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>договор</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>учет</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>модель</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>заказано</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>документы</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>цех</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>статус</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>дата отправки</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>кол-во</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>мест</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>вес</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>сумма отправки</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>документы отправки</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>водитель</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>сумма заказа</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>предоплата</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>фактическая постоплата</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>предполагаемая постоплата</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>недоплата</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>доп постоплата</t>
-        </is>
+    <row r="1" spans="1:22" ht="42" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Аи 13.04.26/4</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>666/1-1</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Костюм_руб_с_кор_рук_и_шорт_Учет_Бишкек_NEW_Айзада_Az.pdf</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>костюм летний с шортами сингапур</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+    <row r="2" spans="1:22" ht="34" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2">
         <v>750</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="5">
         <v>400</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Аи 13.04.26/4_666</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>отправлено</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>05.06.2026</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2">
         <v>812</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="2">
         <v>8</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="2">
         <v>282</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="N2" s="5">
         <v>324800</v>
       </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>отправка 666.pdf</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>Ташыкулов Элмир Койчубаевич</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="n">
+      <c r="O2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="5">
         <v>300000</v>
       </c>
-      <c r="R2" s="5" t="n">
+      <c r="R2" s="5">
         <v>150000</v>
       </c>
-      <c r="S2" s="5" t="n">
+      <c r="S2" s="5">
         <v>174800</v>
       </c>
       <c r="T2" s="5">
         <f>VALUE(SUBSTITUTE(N2," ",""))-VALUE(SUBSTITUTE(R2," ",""))</f>
-        <v/>
+        <v>174800</v>
       </c>
       <c r="U2" s="5">
         <f>VALUE(SUBSTITUTE(T2," ",""))-VALUE(SUBSTITUTE(S2," ",""))</f>
-        <v/>
-      </c>
-      <c r="V2" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="V2" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1000">
       <formula1>"Нурлан,Майрам,Венера,Дача-Суу,Сулайман"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId3"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="G2" r:id="rId2"/>
+    <hyperlink ref="O2" r:id="rId3"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>